--- a/artfynd/A 25040-2026 artfynd.xlsx
+++ b/artfynd/A 25040-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>221312</v>
+        <v>219767</v>
       </c>
       <c r="B2" t="n">
-        <v>97654</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572889.6266158031</v>
+        <v>572890</v>
       </c>
       <c r="R2" t="n">
-        <v>6855726.760275936</v>
+        <v>6855727</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1983-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1983-07-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>NAT_NA SKOGSSVINGEL 4.  Tot_Ha 4,9.   SignArt 0139.   Inv.period (inv. 1995-2003)</t>
+          <t>Följ bäcken mot Ör(?)tjärn.  Liten lokal med rik flora vid bäck. Lövdunge omgiven av barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +767,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>LÖVSKOG</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -791,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Arnold Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
